--- a/docs/equipement.xlsx
+++ b/docs/equipement.xlsx
@@ -295,7 +295,7 @@
     <t>TALISMAN ★</t>
   </si>
   <si>
-    <t>amulette, fétiche, idole, sceau, sigil, totem, relique, fragment, ossuaire, grigri, charme, insigne, emblème, reliquaire</t>
+    <t>fétiche, sceau, sigil, totem, fragment, ossuaire, grigri, charme, emblème, reliquaire</t>
   </si>
   <si>
     <t>Resistance FEU : 1% / 25%
@@ -310,23 +310,23 @@
 FEU = « ignifuge »
 EAU = « hydrophobe »
 FOUDRE = « paratonnerre »
-TERRE = « aérien(ne) »
-FEU + EAU = « vaporeux(se) »
+TERRE = « aérien »
+FEU + EAU = « vaporeux »
 FEU + FOUDRE = « cataclysmique »
 FEU + TERRE = « volcanique »
 FEU + SACRE = « de foi »
-FEU + TENEBRES = « infernal(e) »
+FEU + TENEBRES = « infernal »
 EAU + FOUDRE = « de conduction »
 EAU + TERRE = « de vie »
-EAU + SACRE = « béni(e) »
-EAU + TENEBRES = « pesteux(se) »
+EAU + SACRE = « béni »
+EAU + TENEBRES = « pesteux»
 FOUDRE + TERRE = « tellurique »
-FOUDRE + SACRE = « divin(e) »
-FOUDRE + TENEBRES = « abyssal(e) »
-TERRE + SACRE = « consacré(e) »
-TERRE + TENEBRES = « rampant(e) »
+FOUDRE + SACRE = « divin »
+FOUDRE + TENEBRES = « abyssal »
+TERRE + SACRE = « consacré »
+TERRE + TENEBRES = « rampant »
 SACRE + TENEBRES = « d’humanité »
-3 ELEMENTS = « amalgamé(e) »
+3 ELEMENTS = « amalgamé »
 4 ELEMENTS = « chromatique »</t>
   </si>
   <si>

--- a/docs/equipement.xlsx
+++ b/docs/equipement.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>Tableau 1</t>
   </si>
@@ -79,9 +79,9 @@
 « De feu », « de foudre », etc…</t>
   </si>
   <si>
-    <t>-Arme inerte (x1)
--Gabarit (30% 0, 60% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
+    <t>-Arme inerte (x1) 75%
+-Gabarit selon rang 60%
+-Catalyseur (45%, selon rareté)</t>
   </si>
   <si>
     <t xml:space="preserve">(Dégâts * rang * rareté) / 2
@@ -91,11 +91,6 @@
     <t>ARMES ★★</t>
   </si>
   <si>
-    <t>-Arme inerte (x1)
--Gabarit (25% 0, 35% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMES ★★★</t>
   </si>
   <si>
@@ -105,19 +100,9 @@
     <t>OUI (40% NON, 10% CHAQUE ELEMENT)</t>
   </si>
   <si>
-    <t>-Arme inerte (x1)
--Gabarit (20% 0, 65% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMES ★★★★</t>
   </si>
   <si>
-    <t>-Arme inerte (x1)
--Gabarit (15% 0, 70% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMES ★★★★★</t>
   </si>
   <si>
@@ -125,11 +110,6 @@
   </si>
   <si>
     <t>DEGATS + 3</t>
-  </si>
-  <si>
-    <t>-Arme inerte (x1)
--Gabarit (10% 0, 65% 1, 25% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
   </si>
   <si>
     <t>ARMURES ★</t>
@@ -161,9 +141,9 @@
 REC = « de soins »</t>
   </si>
   <si>
-    <t>-Armure inerte (x1)
--Gabarit (30% 0, 60% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
+    <t>-Armure inerte (x1) 75%
+-Gabarit selon rang 60%
+-Catalyseur (45%, selon rareté)</t>
   </si>
   <si>
     <t xml:space="preserve">(20 * rang * rareté) / 2
@@ -173,42 +153,22 @@
     <t>ARMURES ★★</t>
   </si>
   <si>
-    <t>-Armure inerte (x1)
--Gabarit (25% 0, 35% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMURES ★★★</t>
   </si>
   <si>
     <t>PV + 2</t>
   </si>
   <si>
-    <t>-Armure inerte (x1)
--Gabarit (20% 0, 65% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMURES ★★★★</t>
   </si>
   <si>
     <t>PV + 3</t>
   </si>
   <si>
-    <t>-Armure inerte (x1)
--Gabarit (15% 0, 70% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ARMURES ★★★★★</t>
   </si>
   <si>
     <t>PV + 4</t>
-  </si>
-  <si>
-    <t>-Armure inerte (x1)
--Gabarit (10% 0, 65% 1, 25% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
   </si>
   <si>
     <t>ACCESSOIRES ★</t>
@@ -246,50 +206,30 @@
 REL = « de concentration »</t>
   </si>
   <si>
-    <t>-Accessoire inerte (x1)
--Gabarit (30% 0, 60% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
+    <t>-Accessoire inerte (x1) 75%
+-Gabarit selon rang 60%
+-Catalyseur (45%, selon rareté)</t>
   </si>
   <si>
     <t>ACCESSOIRES ★★</t>
   </si>
   <si>
-    <t>-Accessoire inerte (x1)
--Gabarit (25% 0, 35% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ACCESSOIRES ★★★</t>
   </si>
   <si>
     <t>2+1</t>
   </si>
   <si>
-    <t>-Accessoire inerte (x1)
--Gabarit (20% 0, 65% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ACCESSOIRES ★★★★</t>
   </si>
   <si>
     <t>2+2</t>
   </si>
   <si>
-    <t>-Accessoire inerte (x1)
--Gabarit (15% 0, 70% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>ACCESSOIRES ★★★★★</t>
   </si>
   <si>
     <t>3+2</t>
-  </si>
-  <si>
-    <t>-Accessoire inerte (x1)
--Gabarit (10% 0, 65% 1, 25% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
   </si>
   <si>
     <t>TALISMAN ★</t>
@@ -330,41 +270,21 @@
 4 ELEMENTS = « chromatique »</t>
   </si>
   <si>
-    <t>-Talisman inerte(x1)
--Gabarit (30% 0, 60% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
+    <t>-Talisman inerte (x1) 75%
+-Gabarit selon rang 60%
+-Catalyseur (45%, selon rareté)</t>
   </si>
   <si>
     <t>TALISMAN ★★</t>
   </si>
   <si>
-    <t>-Talisman inerte(x1)
--Gabarit (25% 0, 35% 1, 10% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>TALISMAN ★★★</t>
   </si>
   <si>
-    <t>-Talisman inerte(x1)
--Gabarit (20% 0, 65% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>TALISMAN ★★★★</t>
   </si>
   <si>
-    <t>-Talisman inerte(x1)
--Gabarit (15% 0, 70% 1, 15% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
-  </si>
-  <si>
     <t>TALISMAN ★★★★★</t>
-  </si>
-  <si>
-    <t>-Talisman inerte(x1)
--Gabarit (10% 0, 65% 1, 25% 2) selon rang,
--Catalyseur (33%, selon rareté)</t>
   </si>
 </sst>
 </file>
@@ -1813,7 +1733,7 @@
       </c>
       <c r="H4" s="14"/>
       <c r="I4" t="s" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -1821,23 +1741,23 @@
     </row>
     <row r="5" ht="56.05" customHeight="1">
       <c r="A5" t="s" s="12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" t="s" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="17">
         <v>0.25</v>
       </c>
       <c r="G5" t="s" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="14"/>
       <c r="I5" t="s" s="15">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -1845,23 +1765,23 @@
     </row>
     <row r="6" ht="56.05" customHeight="1">
       <c r="A6" t="s" s="12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" t="s" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="17">
         <v>1</v>
       </c>
       <c r="G6" t="s" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" t="s" s="15">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
@@ -1869,27 +1789,27 @@
     </row>
     <row r="7" ht="68.05" customHeight="1">
       <c r="A7" t="s" s="12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s" s="18">
         <v>12</v>
       </c>
       <c r="C7" t="s" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" t="s" s="15">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7" s="17">
         <v>2</v>
       </c>
       <c r="G7" t="s" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" t="s" s="15">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
@@ -1897,19 +1817,19 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="12">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s" s="18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s" s="15">
         <v>12</v>
       </c>
       <c r="D8" t="s" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s" s="15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F8" s="19">
         <v>0</v>
@@ -1918,26 +1838,26 @@
         <v>12</v>
       </c>
       <c r="H8" t="s" s="15">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I8" t="s" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
     </row>
     <row r="9" ht="56.05" customHeight="1">
       <c r="A9" t="s" s="12">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" t="s" s="15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F9" s="16">
         <v>0.1</v>
@@ -1945,7 +1865,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
       <c r="I9" t="s" s="15">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
@@ -1953,13 +1873,13 @@
     </row>
     <row r="10" ht="56.05" customHeight="1">
       <c r="A10" t="s" s="12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" t="s" s="15">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F10" s="17">
         <v>0.25</v>
@@ -1967,7 +1887,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
       <c r="I10" t="s" s="15">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
@@ -1975,13 +1895,13 @@
     </row>
     <row r="11" ht="56.05" customHeight="1">
       <c r="A11" t="s" s="12">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" t="s" s="15">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F11" s="17">
         <v>1</v>
@@ -1989,7 +1909,7 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" t="s" s="15">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
@@ -1997,13 +1917,13 @@
     </row>
     <row r="12" ht="56.05" customHeight="1">
       <c r="A12" t="s" s="12">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" t="s" s="15">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F12" s="17">
         <v>2</v>
@@ -2011,7 +1931,7 @@
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
       <c r="I12" t="s" s="15">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
@@ -2019,19 +1939,19 @@
     </row>
     <row r="13" ht="56.05" customHeight="1">
       <c r="A13" t="s" s="12">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="18">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="15">
         <v>12</v>
       </c>
       <c r="D13" t="s" s="15">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s" s="15">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13" s="19">
         <v>0</v>
@@ -2040,26 +1960,26 @@
         <v>12</v>
       </c>
       <c r="H13" t="s" s="15">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s" s="15">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" ht="56.05" customHeight="1">
       <c r="A14" t="s" s="12">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" t="s" s="15">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F14" s="16">
         <v>0.1</v>
@@ -2067,7 +1987,7 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" t="s" s="15">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
@@ -2075,13 +1995,13 @@
     </row>
     <row r="15" ht="56.05" customHeight="1">
       <c r="A15" t="s" s="12">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" t="s" s="15">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F15" s="17">
         <v>0.25</v>
@@ -2089,7 +2009,7 @@
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" t="s" s="15">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
@@ -2097,13 +2017,13 @@
     </row>
     <row r="16" ht="56.05" customHeight="1">
       <c r="A16" t="s" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" t="s" s="15">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F16" s="17">
         <v>1</v>
@@ -2111,7 +2031,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
       <c r="I16" t="s" s="15">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
@@ -2119,13 +2039,13 @@
     </row>
     <row r="17" ht="56.05" customHeight="1">
       <c r="A17" t="s" s="12">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" t="s" s="15">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F17" s="17">
         <v>2</v>
@@ -2133,7 +2053,7 @@
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" t="s" s="15">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="14"/>
@@ -2141,16 +2061,16 @@
     </row>
     <row r="18" ht="56.05" customHeight="1">
       <c r="A18" t="s" s="12">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="18">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s" s="15">
         <v>12</v>
       </c>
       <c r="D18" t="s" s="15">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E18" s="19">
         <v>1</v>
@@ -2162,20 +2082,20 @@
         <v>12</v>
       </c>
       <c r="H18" t="s" s="15">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I18" t="s" s="15">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J18" t="s" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" ht="56.05" customHeight="1">
       <c r="A19" t="s" s="12">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
@@ -2189,7 +2109,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" t="s" s="15">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
@@ -2197,7 +2117,7 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="12">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
@@ -2211,7 +2131,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" t="s" s="15">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
@@ -2219,7 +2139,7 @@
     </row>
     <row r="21" ht="56.05" customHeight="1">
       <c r="A21" t="s" s="12">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="14"/>
@@ -2233,7 +2153,7 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" t="s" s="15">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
@@ -2241,7 +2161,7 @@
     </row>
     <row r="22" ht="56.05" customHeight="1">
       <c r="A22" t="s" s="12">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="14"/>
@@ -2255,7 +2175,7 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" t="s" s="15">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
